--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,191 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E8" s="3">
         <v>8200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5500</v>
       </c>
       <c r="J8" s="3">
         <v>5500</v>
       </c>
       <c r="K8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="L8" s="3">
         <v>5700</v>
-      </c>
-      <c r="L8" s="3">
-        <v>5600</v>
       </c>
       <c r="M8" s="3">
         <v>5600</v>
       </c>
       <c r="N8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="O8" s="3">
         <v>22400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5700</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5500</v>
       </c>
       <c r="Q8" s="3">
         <v>5500</v>
       </c>
       <c r="R8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S8" s="3">
         <v>5600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,25 +1362,26 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>700</v>
       </c>
       <c r="I17" s="3">
         <v>700</v>
@@ -1363,129 +1390,135 @@
         <v>700</v>
       </c>
       <c r="K17" s="3">
+        <v>700</v>
+      </c>
+      <c r="L17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1200</v>
       </c>
       <c r="V17" s="3">
         <v>1200</v>
       </c>
       <c r="W17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X17" s="3">
         <v>900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E18" s="3">
         <v>5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>4800</v>
       </c>
       <c r="J18" s="3">
         <v>4800</v>
       </c>
       <c r="K18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="L18" s="3">
         <v>4900</v>
       </c>
       <c r="M18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N18" s="3">
         <v>4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4200</v>
-      </c>
-      <c r="T18" s="3">
-        <v>3800</v>
       </c>
       <c r="U18" s="3">
         <v>3800</v>
       </c>
       <c r="V18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W18" s="3">
         <v>3700</v>
-      </c>
-      <c r="W18" s="3">
-        <v>3800</v>
       </c>
       <c r="X18" s="3">
         <v>3800</v>
       </c>
       <c r="Y18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z18" s="3">
         <v>3600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,82 +1545,86 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2900</v>
       </c>
       <c r="I20" s="3">
         <v>-2900</v>
       </c>
       <c r="J20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-2400</v>
       </c>
       <c r="T20" s="3">
         <v>-2400</v>
       </c>
       <c r="U20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="V20" s="3">
         <v>-2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1657,11 +1694,14 @@
       <c r="Y21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1734,93 +1774,99 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1800</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1400</v>
       </c>
       <c r="U23" s="3">
         <v>1400</v>
       </c>
       <c r="V23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W23" s="3">
         <v>1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
@@ -1829,37 +1875,37 @@
         <v>500</v>
       </c>
       <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>400</v>
       </c>
       <c r="L24" s="3">
         <v>400</v>
       </c>
       <c r="M24" s="3">
+        <v>400</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
-      </c>
-      <c r="P24" s="3">
-        <v>300</v>
       </c>
       <c r="Q24" s="3">
         <v>300</v>
       </c>
       <c r="R24" s="3">
+        <v>300</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>300</v>
       </c>
       <c r="T24" s="3">
         <v>300</v>
@@ -1868,22 +1914,25 @@
         <v>300</v>
       </c>
       <c r="V24" s="3">
+        <v>300</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E26" s="3">
         <v>2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1500</v>
       </c>
       <c r="J26" s="3">
         <v>1500</v>
       </c>
       <c r="K26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>1100</v>
       </c>
       <c r="Y26" s="3">
         <v>1100</v>
       </c>
       <c r="Z26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2200</v>
       </c>
       <c r="F27" s="3">
         <v>2200</v>
       </c>
       <c r="G27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H27" s="3">
         <v>2300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1800</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1500</v>
       </c>
       <c r="J27" s="3">
         <v>1500</v>
       </c>
       <c r="K27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
-      </c>
-      <c r="X27" s="3">
-        <v>1100</v>
       </c>
       <c r="Y27" s="3">
         <v>1100</v>
       </c>
       <c r="Z27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E32" s="3">
         <v>3300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2900</v>
       </c>
       <c r="I32" s="3">
         <v>2900</v>
       </c>
       <c r="J32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K32" s="3">
         <v>3000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2600</v>
-      </c>
-      <c r="S32" s="3">
-        <v>2400</v>
       </c>
       <c r="T32" s="3">
         <v>2400</v>
       </c>
       <c r="U32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="V32" s="3">
         <v>2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1900</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2200</v>
       </c>
       <c r="F33" s="3">
         <v>2200</v>
       </c>
       <c r="G33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H33" s="3">
         <v>2300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1500</v>
       </c>
       <c r="J33" s="3">
         <v>1500</v>
       </c>
       <c r="K33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>1100</v>
       </c>
       <c r="Y33" s="3">
         <v>1100</v>
       </c>
       <c r="Z33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1900</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2200</v>
       </c>
       <c r="F35" s="3">
         <v>2200</v>
       </c>
       <c r="G35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H35" s="3">
         <v>2300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1500</v>
       </c>
       <c r="J35" s="3">
         <v>1500</v>
       </c>
       <c r="K35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>1100</v>
       </c>
       <c r="Y35" s="3">
         <v>1100</v>
       </c>
       <c r="Z35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,156 +2917,163 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E41" s="3">
         <v>10000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>6900</v>
       </c>
       <c r="R41" s="3">
         <v>6900</v>
       </c>
       <c r="S41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="T41" s="3">
         <v>9100</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>8600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7400</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E42" s="3">
         <v>69300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>65100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>92400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>113000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>143900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>163500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>136600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>133600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>120800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>131400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>91400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>59300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>27300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>22800</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U42" s="3">
+      <c r="U42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V42" s="3">
         <v>15900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6300</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3201,8 +3300,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3284,62 +3389,62 @@
         <v>3000</v>
       </c>
       <c r="E47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F47" s="3">
         <v>2900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2800</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2700</v>
       </c>
       <c r="H47" s="3">
         <v>2700</v>
       </c>
       <c r="I47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J47" s="3">
         <v>2600</v>
-      </c>
-      <c r="J47" s="3">
-        <v>2400</v>
       </c>
       <c r="K47" s="3">
         <v>2400</v>
       </c>
       <c r="L47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M47" s="3">
         <v>2300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2100</v>
       </c>
       <c r="O47" s="3">
         <v>2100</v>
       </c>
       <c r="P47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="Q47" s="3">
         <v>2000</v>
       </c>
       <c r="R47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S47" s="3">
         <v>1900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1800</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>1800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3349,8 +3454,11 @@
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3358,10 +3466,10 @@
         <v>14500</v>
       </c>
       <c r="E48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F48" s="3">
         <v>14600</v>
-      </c>
-      <c r="F48" s="3">
-        <v>14100</v>
       </c>
       <c r="G48" s="3">
         <v>14100</v>
@@ -3370,61 +3478,64 @@
         <v>14100</v>
       </c>
       <c r="I48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="J48" s="3">
         <v>14200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>14400</v>
       </c>
       <c r="K48" s="3">
         <v>14400</v>
       </c>
       <c r="L48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="M48" s="3">
         <v>13900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>13600</v>
       </c>
       <c r="P48" s="3">
         <v>13600</v>
       </c>
       <c r="Q48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="R48" s="3">
         <v>13500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12900</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>12400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>741900</v>
+      </c>
+      <c r="E54" s="3">
         <v>746800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>714800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>715500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>707000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>717400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>700500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>663800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>655100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>645300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>641100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>597800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>586700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>576700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>513100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>492800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>484600</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>457700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>434800</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,8 +4053,9 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3934,71 +4065,74 @@
       <c r="E57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,8 +4205,11 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4145,8 +4282,11 @@
       <c r="Z59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4228,7 +4371,7 @@
         <v>14000</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4240,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>3000</v>
@@ -4249,7 +4392,7 @@
         <v>3000</v>
       </c>
       <c r="L61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="M61" s="3">
         <v>4000</v>
@@ -4261,19 +4404,19 @@
         <v>4000</v>
       </c>
       <c r="P61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="Q61" s="3">
         <v>10000</v>
       </c>
       <c r="R61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="S61" s="3">
         <v>5000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4291,10 +4434,13 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>670800</v>
+      </c>
+      <c r="E66" s="3">
         <v>676700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>646200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>649100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>649000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>659900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>641100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>604600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>596600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>588500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>585600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>544000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>533700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>524600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>461900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>442500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>435100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>410500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>388500</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4854,7 +5022,7 @@
         <v>200</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E72" s="3">
         <v>50500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>48900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>45800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>43900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>42500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>41300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>43600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>42400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>40700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>39700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>38900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>37300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36300</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>34300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>33300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E76" s="3">
         <v>69900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>68300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>57900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>57600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>59500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>58600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>56900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>55500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>51100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>50300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49500</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>47200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>46300</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1900</v>
-      </c>
-      <c r="E81" s="3">
-        <v>2200</v>
       </c>
       <c r="F81" s="3">
         <v>2200</v>
       </c>
       <c r="G81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="H81" s="3">
         <v>2300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1500</v>
       </c>
       <c r="J81" s="3">
         <v>1500</v>
       </c>
       <c r="K81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>1100</v>
       </c>
       <c r="Y81" s="3">
         <v>1100</v>
       </c>
       <c r="Z81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5680,14 +5879,17 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6124,14 +6341,17 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6226,14 +6447,17 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6448,14 +6678,17 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6846,14 +7092,17 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6926,8 +7175,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6994,10 +7246,13 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,198 +656,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E8" s="3">
         <v>24800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5800</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5500</v>
       </c>
       <c r="K8" s="3">
         <v>5500</v>
       </c>
       <c r="L8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="M8" s="3">
         <v>5700</v>
-      </c>
-      <c r="M8" s="3">
-        <v>5600</v>
       </c>
       <c r="N8" s="3">
         <v>5600</v>
       </c>
       <c r="O8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="P8" s="3">
         <v>22400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5500</v>
       </c>
       <c r="R8" s="3">
         <v>5500</v>
       </c>
       <c r="S8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="T8" s="3">
         <v>5600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -923,8 +929,11 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1000,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1041,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1119,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,8 +1199,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1260,8 +1279,11 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1337,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,28 +1388,29 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E17" s="3">
         <v>6700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>700</v>
       </c>
       <c r="J17" s="3">
         <v>700</v>
@@ -1393,132 +1419,138 @@
         <v>700</v>
       </c>
       <c r="L17" s="3">
+        <v>700</v>
+      </c>
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1200</v>
       </c>
       <c r="W17" s="3">
         <v>1200</v>
       </c>
       <c r="X17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y17" s="3">
         <v>900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E18" s="3">
         <v>18100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>4800</v>
       </c>
       <c r="K18" s="3">
         <v>4800</v>
       </c>
       <c r="L18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="M18" s="3">
         <v>4900</v>
       </c>
       <c r="N18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="O18" s="3">
         <v>4800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4200</v>
-      </c>
-      <c r="U18" s="3">
-        <v>3800</v>
       </c>
       <c r="V18" s="3">
         <v>3800</v>
       </c>
       <c r="W18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X18" s="3">
         <v>3700</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3800</v>
       </c>
       <c r="Y18" s="3">
         <v>3800</v>
       </c>
       <c r="Z18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA18" s="3">
         <v>3600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,85 +1578,89 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2900</v>
       </c>
       <c r="J20" s="3">
         <v>-2900</v>
       </c>
       <c r="K20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="L20" s="3">
         <v>-3000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-2400</v>
       </c>
       <c r="U20" s="3">
         <v>-2400</v>
       </c>
       <c r="V20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1697,11 +1733,14 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1777,99 +1816,105 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E23" s="3">
         <v>8000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1800</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1400</v>
       </c>
       <c r="V23" s="3">
         <v>1400</v>
       </c>
       <c r="W23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X23" s="3">
         <v>1000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>1600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>500</v>
@@ -1878,37 +1923,37 @@
         <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>400</v>
       </c>
       <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
+        <v>300</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
       </c>
       <c r="U24" s="3">
         <v>300</v>
@@ -1917,22 +1962,25 @@
         <v>300</v>
       </c>
       <c r="W24" s="3">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>300</v>
       </c>
       <c r="Y24" s="3">
         <v>300</v>
       </c>
       <c r="Z24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E26" s="3">
         <v>6400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1500</v>
       </c>
       <c r="K26" s="3">
         <v>1500</v>
       </c>
       <c r="L26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M26" s="3">
         <v>1800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>1100</v>
       </c>
       <c r="Z26" s="3">
         <v>1100</v>
       </c>
       <c r="AA26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>6000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2200</v>
       </c>
       <c r="G27" s="3">
         <v>2200</v>
       </c>
       <c r="H27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I27" s="3">
         <v>2300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1800</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1500</v>
       </c>
       <c r="K27" s="3">
         <v>1500</v>
       </c>
       <c r="L27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>1100</v>
       </c>
       <c r="Z27" s="3">
         <v>1100</v>
       </c>
       <c r="AA27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2536,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>10100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2900</v>
       </c>
       <c r="J32" s="3">
         <v>2900</v>
       </c>
       <c r="K32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L32" s="3">
         <v>3000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>2400</v>
       </c>
       <c r="U32" s="3">
         <v>2400</v>
       </c>
       <c r="V32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>6000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1900</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2200</v>
       </c>
       <c r="G33" s="3">
         <v>2200</v>
       </c>
       <c r="H33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I33" s="3">
         <v>2300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1500</v>
       </c>
       <c r="K33" s="3">
         <v>1500</v>
       </c>
       <c r="L33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>1100</v>
       </c>
       <c r="Z33" s="3">
         <v>1100</v>
       </c>
       <c r="AA33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>6000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1900</v>
-      </c>
-      <c r="F35" s="3">
-        <v>2200</v>
       </c>
       <c r="G35" s="3">
         <v>2200</v>
       </c>
       <c r="H35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I35" s="3">
         <v>2300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1500</v>
       </c>
       <c r="K35" s="3">
         <v>1500</v>
       </c>
       <c r="L35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>1100</v>
       </c>
       <c r="Z35" s="3">
         <v>1100</v>
       </c>
       <c r="AA35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,162 +3003,169 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E41" s="3">
         <v>11100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
-      </c>
-      <c r="R41" s="3">
-        <v>6900</v>
       </c>
       <c r="S41" s="3">
         <v>6900</v>
       </c>
       <c r="T41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="U41" s="3">
         <v>9100</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>8600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7400</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E42" s="3">
         <v>44000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>69300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>65100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>92400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>113000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>143900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>163500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>136600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>133600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>120800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>131400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>91400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>72300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>27300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>20300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>22800</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V42" s="3">
+      <c r="V42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
         <v>15900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6300</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3149,8 +3241,11 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,8 +3321,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3303,8 +3401,11 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3380,74 +3481,77 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>3000</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
         <v>3000</v>
       </c>
       <c r="F47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G47" s="3">
         <v>2900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2700</v>
       </c>
       <c r="I47" s="3">
         <v>2700</v>
       </c>
       <c r="J47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K47" s="3">
         <v>2600</v>
-      </c>
-      <c r="K47" s="3">
-        <v>2400</v>
       </c>
       <c r="L47" s="3">
         <v>2400</v>
       </c>
       <c r="M47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="N47" s="3">
         <v>2300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2100</v>
       </c>
       <c r="P47" s="3">
         <v>2100</v>
       </c>
       <c r="Q47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="R47" s="3">
         <v>2000</v>
       </c>
       <c r="S47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T47" s="3">
         <v>1900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1800</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>1800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1700</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3457,22 +3561,25 @@
       <c r="AA47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>14500</v>
+        <v>14700</v>
       </c>
       <c r="E48" s="3">
         <v>14500</v>
       </c>
       <c r="F48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="G48" s="3">
         <v>14600</v>
-      </c>
-      <c r="G48" s="3">
-        <v>14100</v>
       </c>
       <c r="H48" s="3">
         <v>14100</v>
@@ -3481,61 +3588,64 @@
         <v>14100</v>
       </c>
       <c r="J48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K48" s="3">
         <v>14200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>14400</v>
       </c>
       <c r="L48" s="3">
         <v>14400</v>
       </c>
       <c r="M48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="N48" s="3">
         <v>13900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>13600</v>
       </c>
       <c r="Q48" s="3">
         <v>13600</v>
       </c>
       <c r="R48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="S48" s="3">
         <v>13500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12900</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>12400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11900</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3611,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3881,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3842,8 +3961,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4041,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>789000</v>
+      </c>
+      <c r="E54" s="3">
         <v>741900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>746800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>714800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>715500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>707000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>717400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>700500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>663800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>655100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>645300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>641100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>597800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>586700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>576700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>513100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>492800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>484600</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>457700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>434800</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,13 +4183,14 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>1600</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>5</v>
@@ -4068,71 +4198,74 @@
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4208,8 +4341,11 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4285,8 +4421,11 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4362,19 +4501,22 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="E61" s="3">
         <v>14000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -4386,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>3000</v>
@@ -4395,7 +4537,7 @@
         <v>3000</v>
       </c>
       <c r="M61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="N61" s="3">
         <v>4000</v>
@@ -4407,19 +4549,19 @@
         <v>4000</v>
       </c>
       <c r="Q61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="R61" s="3">
         <v>10000</v>
       </c>
       <c r="S61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="T61" s="3">
         <v>5000</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -4437,10 +4579,13 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4516,8 +4661,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4901,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>714200</v>
+      </c>
+      <c r="E66" s="3">
         <v>670800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>676700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>646200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>649100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>649000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>659900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>641100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>604600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>596600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>588500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>585600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>544000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>533700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>524600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>461900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>442500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>435100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>410500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>388500</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5025,7 +5192,7 @@
         <v>200</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -5084,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5331,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E72" s="3">
         <v>52100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>50500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>48900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>47700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>45800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>43900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>42500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>41300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>40700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>39700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>38900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>37300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>36300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>34300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>33300</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5651,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E76" s="3">
         <v>70800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>69900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>57900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>57600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>59500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>56900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>53800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>52200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>51100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>50300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>47200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>46300</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>6000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1900</v>
-      </c>
-      <c r="F81" s="3">
-        <v>2200</v>
       </c>
       <c r="G81" s="3">
         <v>2200</v>
       </c>
       <c r="H81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I81" s="3">
         <v>2300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1500</v>
       </c>
       <c r="K81" s="3">
         <v>1500</v>
       </c>
       <c r="L81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>1100</v>
       </c>
       <c r="Z81" s="3">
         <v>1100</v>
       </c>
       <c r="AA81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,8 +6008,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5882,14 +6080,17 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,8 +6486,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6344,14 +6560,17 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6598,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6450,14 +6670,17 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,8 +6836,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6681,14 +6910,17 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6793,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,8 +7266,11 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7095,14 +7340,17 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7178,8 +7426,11 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7249,10 +7500,13 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,204 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E8" s="3">
         <v>9600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24800</v>
       </c>
-      <c r="F8" s="3">
-        <v>8200</v>
-      </c>
       <c r="G8" s="3">
+        <v>16100</v>
+      </c>
+      <c r="H8" s="3">
         <v>7800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5800</v>
-      </c>
-      <c r="K8" s="3">
-        <v>5500</v>
       </c>
       <c r="L8" s="3">
         <v>5500</v>
       </c>
       <c r="M8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="N8" s="3">
         <v>5700</v>
-      </c>
-      <c r="N8" s="3">
-        <v>5600</v>
       </c>
       <c r="O8" s="3">
         <v>5600</v>
       </c>
       <c r="P8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="Q8" s="3">
         <v>22400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>5500</v>
       </c>
       <c r="S8" s="3">
         <v>5500</v>
       </c>
       <c r="T8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="U8" s="3">
         <v>5600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -932,8 +939,11 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,8 +1055,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1122,8 +1136,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,8 +1219,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1282,8 +1302,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,31 +1415,32 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6700</v>
       </c>
-      <c r="F17" s="3">
-        <v>2400</v>
-      </c>
       <c r="G17" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>700</v>
       </c>
       <c r="K17" s="3">
         <v>700</v>
@@ -1422,135 +1449,141 @@
         <v>700</v>
       </c>
       <c r="M17" s="3">
+        <v>700</v>
+      </c>
+      <c r="N17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
-      </c>
-      <c r="W17" s="3">
-        <v>1200</v>
       </c>
       <c r="X17" s="3">
         <v>1200</v>
       </c>
       <c r="Y17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z17" s="3">
         <v>900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E18" s="3">
         <v>6000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18100</v>
       </c>
-      <c r="F18" s="3">
-        <v>5800</v>
-      </c>
       <c r="G18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H18" s="3">
         <v>6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>4800</v>
       </c>
       <c r="L18" s="3">
         <v>4800</v>
       </c>
       <c r="M18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="N18" s="3">
         <v>4900</v>
       </c>
       <c r="O18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="P18" s="3">
         <v>4800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4200</v>
-      </c>
-      <c r="V18" s="3">
-        <v>3800</v>
       </c>
       <c r="W18" s="3">
         <v>3800</v>
       </c>
       <c r="X18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y18" s="3">
         <v>3700</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3800</v>
       </c>
       <c r="Z18" s="3">
         <v>3800</v>
       </c>
       <c r="AA18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,88 +1612,92 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-10100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2900</v>
       </c>
       <c r="K20" s="3">
         <v>-2900</v>
       </c>
       <c r="L20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="M20" s="3">
         <v>-3000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-2400</v>
       </c>
       <c r="V20" s="3">
         <v>-2400</v>
       </c>
       <c r="W20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="X20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1736,11 +1773,14 @@
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1819,105 +1859,111 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>2200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="G23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="Q23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="S23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="V23" s="3">
         <v>1800</v>
-      </c>
-      <c r="M23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2000</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="P23" s="3">
-        <v>5800</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1400</v>
       </c>
       <c r="W23" s="3">
         <v>1400</v>
       </c>
       <c r="X23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
-        <v>500</v>
-      </c>
       <c r="G24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H24" s="3">
         <v>600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
       </c>
       <c r="I24" s="3">
         <v>500</v>
@@ -1926,37 +1972,37 @@
         <v>500</v>
       </c>
       <c r="K24" s="3">
+        <v>500</v>
+      </c>
+      <c r="L24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
-      </c>
-      <c r="M24" s="3">
-        <v>400</v>
       </c>
       <c r="N24" s="3">
         <v>400</v>
       </c>
       <c r="O24" s="3">
+        <v>400</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
@@ -1965,22 +2011,25 @@
         <v>300</v>
       </c>
       <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>300</v>
       </c>
       <c r="Z24" s="3">
         <v>300</v>
       </c>
       <c r="AA24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,8 +2108,11 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2068,79 +2120,82 @@
         <v>1800</v>
       </c>
       <c r="E26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F26" s="3">
         <v>6400</v>
       </c>
-      <c r="F26" s="3">
-        <v>2000</v>
-      </c>
       <c r="G26" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H26" s="3">
         <v>2300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1800</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1500</v>
       </c>
       <c r="L26" s="3">
         <v>1500</v>
       </c>
       <c r="M26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N26" s="3">
         <v>1800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>1100</v>
       </c>
       <c r="AA26" s="3">
         <v>1100</v>
       </c>
       <c r="AB26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2148,79 +2203,82 @@
         <v>1700</v>
       </c>
       <c r="E27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>6000</v>
       </c>
-      <c r="F27" s="3">
-        <v>1900</v>
-      </c>
       <c r="G27" s="3">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="H27" s="3">
         <v>2200</v>
       </c>
       <c r="I27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1800</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1500</v>
       </c>
       <c r="L27" s="3">
         <v>1500</v>
       </c>
       <c r="M27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N27" s="3">
         <v>1800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>1100</v>
       </c>
       <c r="AA27" s="3">
         <v>1100</v>
       </c>
       <c r="AB27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,88 +2606,94 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>10100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I32" s="3">
         <v>3300</v>
       </c>
-      <c r="G32" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2900</v>
       </c>
       <c r="K32" s="3">
         <v>2900</v>
       </c>
       <c r="L32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M32" s="3">
         <v>3000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2600</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2400</v>
       </c>
       <c r="V32" s="3">
         <v>2400</v>
       </c>
       <c r="W32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="X32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2628,79 +2701,82 @@
         <v>1700</v>
       </c>
       <c r="E33" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>6000</v>
       </c>
-      <c r="F33" s="3">
-        <v>1900</v>
-      </c>
       <c r="G33" s="3">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="H33" s="3">
         <v>2200</v>
       </c>
       <c r="I33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1800</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1500</v>
       </c>
       <c r="L33" s="3">
         <v>1500</v>
       </c>
       <c r="M33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N33" s="3">
         <v>1800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>1100</v>
       </c>
       <c r="AA33" s="3">
         <v>1100</v>
       </c>
       <c r="AB33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,8 +2855,11 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2788,164 +2867,170 @@
         <v>1700</v>
       </c>
       <c r="E35" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>6000</v>
       </c>
-      <c r="F35" s="3">
-        <v>1900</v>
-      </c>
       <c r="G35" s="3">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="H35" s="3">
         <v>2200</v>
       </c>
       <c r="I35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1800</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1500</v>
       </c>
       <c r="L35" s="3">
         <v>1500</v>
       </c>
       <c r="M35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N35" s="3">
         <v>1800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>1100</v>
       </c>
       <c r="AA35" s="3">
         <v>1100</v>
       </c>
       <c r="AB35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,168 +3090,175 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E41" s="3">
         <v>10400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8100</v>
-      </c>
-      <c r="S41" s="3">
-        <v>6900</v>
       </c>
       <c r="T41" s="3">
         <v>6900</v>
       </c>
       <c r="U41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="V41" s="3">
         <v>9100</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>8600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>59600</v>
+      </c>
+      <c r="F42" s="3">
+        <v>44000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>69300</v>
+      </c>
+      <c r="H42" s="3">
+        <v>65100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>92400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>113000</v>
+      </c>
+      <c r="K42" s="3">
+        <v>143900</v>
+      </c>
+      <c r="L42" s="3">
+        <v>163500</v>
+      </c>
+      <c r="M42" s="3">
+        <v>136600</v>
+      </c>
+      <c r="N42" s="3">
+        <v>133600</v>
+      </c>
+      <c r="O42" s="3">
+        <v>120800</v>
+      </c>
+      <c r="P42" s="3">
+        <v>131400</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>91400</v>
+      </c>
+      <c r="R42" s="3">
+        <v>72300</v>
+      </c>
+      <c r="S42" s="3">
         <v>59300</v>
       </c>
-      <c r="E42" s="3">
-        <v>44000</v>
-      </c>
-      <c r="F42" s="3">
-        <v>69300</v>
-      </c>
-      <c r="G42" s="3">
-        <v>65100</v>
-      </c>
-      <c r="H42" s="3">
-        <v>92400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>113000</v>
-      </c>
-      <c r="J42" s="3">
-        <v>143900</v>
-      </c>
-      <c r="K42" s="3">
-        <v>163500</v>
-      </c>
-      <c r="L42" s="3">
-        <v>136600</v>
-      </c>
-      <c r="M42" s="3">
-        <v>133600</v>
-      </c>
-      <c r="N42" s="3">
-        <v>120800</v>
-      </c>
-      <c r="O42" s="3">
-        <v>131400</v>
-      </c>
-      <c r="P42" s="3">
-        <v>91400</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>72300</v>
-      </c>
-      <c r="R42" s="3">
-        <v>59300</v>
-      </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>20300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>22800</v>
       </c>
-      <c r="V42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W42" s="3">
+      <c r="W42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X42" s="3">
         <v>15900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6300</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3244,8 +3337,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3324,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3404,8 +3503,11 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3484,13 +3586,16 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>3100</v>
       </c>
       <c r="E47" s="3">
         <v>3000</v>
@@ -3499,62 +3604,62 @@
         <v>3000</v>
       </c>
       <c r="G47" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H47" s="3">
         <v>2900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>2700</v>
       </c>
       <c r="J47" s="3">
         <v>2700</v>
       </c>
       <c r="K47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L47" s="3">
         <v>2600</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2400</v>
       </c>
       <c r="M47" s="3">
         <v>2400</v>
       </c>
       <c r="N47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="O47" s="3">
         <v>2300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2400</v>
-      </c>
-      <c r="P47" s="3">
-        <v>2100</v>
       </c>
       <c r="Q47" s="3">
         <v>2100</v>
       </c>
       <c r="R47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="S47" s="3">
         <v>2000</v>
       </c>
       <c r="T47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U47" s="3">
         <v>1900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1800</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>1800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3564,25 +3669,28 @@
       <c r="AB47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E48" s="3">
         <v>14700</v>
-      </c>
-      <c r="E48" s="3">
-        <v>14500</v>
       </c>
       <c r="F48" s="3">
         <v>14500</v>
       </c>
       <c r="G48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="H48" s="3">
         <v>14600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>14100</v>
       </c>
       <c r="I48" s="3">
         <v>14100</v>
@@ -3591,61 +3699,64 @@
         <v>14100</v>
       </c>
       <c r="K48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="L48" s="3">
         <v>14200</v>
-      </c>
-      <c r="L48" s="3">
-        <v>14400</v>
       </c>
       <c r="M48" s="3">
         <v>14400</v>
       </c>
       <c r="N48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="O48" s="3">
         <v>13900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>13600</v>
       </c>
       <c r="R48" s="3">
         <v>13600</v>
       </c>
       <c r="S48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="T48" s="3">
         <v>13500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12900</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>12400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,8 +4001,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,88 +4167,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>789000</v>
+        <v>802200</v>
       </c>
       <c r="E54" s="3">
+        <v>791000</v>
+      </c>
+      <c r="F54" s="3">
         <v>741900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>746800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>714800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>715500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>707000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>717400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>700500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>663800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>655100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>645300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>641100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>597800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>586700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>576700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>513100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>492800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>484600</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>457700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>434800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,88 +4314,92 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3">
         <v>300</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4344,8 +4478,11 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4424,8 +4561,11 @@
       <c r="AB59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4504,8 +4644,11 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4513,13 +4656,13 @@
         <v>19000</v>
       </c>
       <c r="E61" s="3">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="F61" s="3">
         <v>14000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4531,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>3000</v>
@@ -4540,7 +4683,7 @@
         <v>3000</v>
       </c>
       <c r="N61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="O61" s="3">
         <v>4000</v>
@@ -4552,19 +4695,19 @@
         <v>4000</v>
       </c>
       <c r="R61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="S61" s="3">
         <v>10000</v>
       </c>
       <c r="T61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="U61" s="3">
         <v>5000</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -4582,10 +4725,13 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,88 +5059,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>714200</v>
+        <v>726100</v>
       </c>
       <c r="E66" s="3">
+        <v>716200</v>
+      </c>
+      <c r="F66" s="3">
         <v>670800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>676700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>646200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>649100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>649000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>659900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>641100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>604600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>596600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>588500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>585600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>544000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>533700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>524600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>461900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>442500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>435100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>410500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>388500</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5195,7 +5363,7 @@
         <v>200</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,88 +5505,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E72" s="3">
         <v>53400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>52100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>50500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>47700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>45800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>43900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>42500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>42400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>40700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>39700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>38900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>38000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>37300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>36300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>34300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>33300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,88 +5837,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>75900</v>
+      </c>
+      <c r="E76" s="3">
         <v>74500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>70800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>69900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>68300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>66100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>57900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>57600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>59500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>59100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>58600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>56900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>53800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>52200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>51100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>50300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49500</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>47200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>46300</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,93 +6003,99 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5908,79 +6103,82 @@
         <v>1700</v>
       </c>
       <c r="E81" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>6000</v>
       </c>
-      <c r="F81" s="3">
-        <v>1900</v>
-      </c>
       <c r="G81" s="3">
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="H81" s="3">
         <v>2200</v>
       </c>
       <c r="I81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1800</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1500</v>
       </c>
       <c r="L81" s="3">
         <v>1500</v>
       </c>
       <c r="M81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N81" s="3">
         <v>1800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>1100</v>
       </c>
       <c r="AA81" s="3">
         <v>1100</v>
       </c>
       <c r="AB81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6083,14 +6282,17 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,8 +6703,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6563,14 +6780,17 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,8 +6819,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6673,14 +6894,17 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,8 +7066,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6913,14 +7143,17 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,8 +7512,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7343,14 +7589,17 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7429,8 +7678,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7503,10 +7755,13 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,211 +656,225 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>9800</v>
+        <v>7500</v>
       </c>
       <c r="E8" s="3">
-        <v>9600</v>
+        <v>7700</v>
       </c>
       <c r="F8" s="3">
-        <v>24800</v>
+        <v>7200</v>
       </c>
       <c r="G8" s="3">
-        <v>16100</v>
+        <v>7100</v>
       </c>
       <c r="H8" s="3">
-        <v>7800</v>
+        <v>7300</v>
       </c>
       <c r="I8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J8" s="3">
         <v>7500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L8" s="3">
         <v>6900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>5600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>22400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>5500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>5600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>5000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>4900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>4700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>4300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,31 +956,37 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7500</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1025,8 +1045,14 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1082,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1139,8 +1167,14 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1222,31 +1256,37 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1305,31 +1345,37 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1388,8 +1434,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1416,43 +1468,45 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3700</v>
+        <v>5000</v>
       </c>
       <c r="E17" s="3">
-        <v>3600</v>
+        <v>4900</v>
       </c>
       <c r="F17" s="3">
-        <v>6700</v>
+        <v>4900</v>
       </c>
       <c r="G17" s="3">
-        <v>4100</v>
+        <v>4500</v>
       </c>
       <c r="H17" s="3">
-        <v>1700</v>
+        <v>4700</v>
       </c>
       <c r="I17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="K17" s="3">
         <v>1500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>700</v>
-      </c>
-      <c r="L17" s="3">
-        <v>700</v>
       </c>
       <c r="M17" s="3">
         <v>700</v>
       </c>
       <c r="N17" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
@@ -1461,22 +1515,22 @@
         <v>800</v>
       </c>
       <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
+        <v>800</v>
+      </c>
+      <c r="S17" s="3">
         <v>6600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
-      </c>
-      <c r="U17" s="3">
-        <v>1500</v>
-      </c>
-      <c r="V17" s="3">
-        <v>1200</v>
       </c>
       <c r="W17" s="3">
         <v>1500</v>
@@ -1485,105 +1539,117 @@
         <v>1200</v>
       </c>
       <c r="Y17" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB17" s="3">
         <v>900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6100</v>
+        <v>2400</v>
       </c>
       <c r="E18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="H18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K18" s="3">
         <v>6000</v>
       </c>
-      <c r="F18" s="3">
-        <v>18100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>6000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>5100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>4800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>15800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>4100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>3800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>4200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>3800</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3700</v>
       </c>
       <c r="Z18" s="3">
         <v>3800</v>
       </c>
       <c r="AA18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>3600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1613,114 +1679,122 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-3800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-3700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-10100</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3">
-        <v>-6700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="I20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-3300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-3000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-2700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-2900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-2100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-2500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-2600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-2400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-2400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-2600</v>
       </c>
       <c r="Z20" s="3">
         <v>-2300</v>
       </c>
       <c r="AA20" s="3">
-        <v>-2400</v>
+        <v>-2600</v>
       </c>
       <c r="AB20" s="3">
         <v>-2300</v>
       </c>
       <c r="AC20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1776,34 +1850,40 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1862,58 +1942,64 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F23" s="3">
         <v>2300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M23" s="3">
         <v>2200</v>
       </c>
-      <c r="F23" s="3">
-        <v>8000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>5400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P23" s="3">
         <v>2200</v>
       </c>
-      <c r="L23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="S23" s="3">
-        <v>1500</v>
       </c>
       <c r="T23" s="3">
         <v>1300</v>
@@ -1922,31 +2008,37 @@
         <v>1500</v>
       </c>
       <c r="V23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="X23" s="3">
         <v>1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1954,82 +2046,88 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F24" s="3">
-        <v>1600</v>
+        <v>500</v>
       </c>
       <c r="G24" s="3">
-        <v>1100</v>
+        <v>500</v>
       </c>
       <c r="H24" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I24" s="3">
         <v>500</v>
       </c>
       <c r="J24" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K24" s="3">
         <v>500</v>
       </c>
       <c r="L24" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M24" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="N24" s="3">
         <v>400</v>
       </c>
       <c r="O24" s="3">
+        <v>300</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
+        <v>400</v>
+      </c>
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>300</v>
-      </c>
-      <c r="T24" s="3">
-        <v>300</v>
-      </c>
-      <c r="U24" s="3">
-        <v>200</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z24" s="3">
         <v>300</v>
       </c>
       <c r="AA24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2111,174 +2209,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F26" s="3">
         <v>1800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1800</v>
       </c>
-      <c r="F26" s="3">
-        <v>6400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>4300</v>
-      </c>
       <c r="H26" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="I26" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J26" s="3">
         <v>2300</v>
       </c>
       <c r="K26" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M26" s="3">
         <v>1800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
-      </c>
-      <c r="S26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1000</v>
       </c>
       <c r="U26" s="3">
         <v>1200</v>
       </c>
       <c r="V26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X26" s="3">
         <v>1500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1100</v>
-      </c>
-      <c r="X26" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>800</v>
       </c>
       <c r="Z26" s="3">
         <v>1200</v>
       </c>
       <c r="AA26" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>1700</v>
       </c>
-      <c r="F27" s="3">
-        <v>6000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>4000</v>
-      </c>
       <c r="H27" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J27" s="3">
         <v>2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
-      </c>
-      <c r="S27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1000</v>
       </c>
       <c r="U27" s="3">
         <v>1200</v>
       </c>
       <c r="V27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X27" s="3">
         <v>1500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1100</v>
-      </c>
-      <c r="X27" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>800</v>
       </c>
       <c r="Z27" s="3">
         <v>1200</v>
       </c>
       <c r="AA27" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC27" s="3">
         <v>1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2360,8 +2476,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2443,8 +2565,14 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2526,8 +2654,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2609,174 +2743,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>3800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>10100</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3">
-        <v>6700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>3200</v>
-      </c>
-      <c r="I32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>3300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>3000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>2700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>2900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>2100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>2500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>2600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>2400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>2400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>2300</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>2600</v>
       </c>
       <c r="Z32" s="3">
         <v>2300</v>
       </c>
       <c r="AA32" s="3">
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="AB32" s="3">
         <v>2300</v>
       </c>
       <c r="AC32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AE32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="3">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="F33" s="3">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="G33" s="3">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="H33" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I33" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J33" s="3">
         <v>2300</v>
       </c>
       <c r="K33" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M33" s="3">
         <v>1800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
-      </c>
-      <c r="S33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1000</v>
       </c>
       <c r="U33" s="3">
         <v>1200</v>
       </c>
       <c r="V33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X33" s="3">
         <v>1500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1100</v>
-      </c>
-      <c r="X33" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>800</v>
       </c>
       <c r="Z33" s="3">
         <v>1200</v>
       </c>
       <c r="AA33" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC33" s="3">
         <v>1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2858,179 +3010,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E35" s="3">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="F35" s="3">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="G35" s="3">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="H35" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I35" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J35" s="3">
         <v>2300</v>
       </c>
       <c r="K35" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M35" s="3">
         <v>1800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
-      </c>
-      <c r="S35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1000</v>
       </c>
       <c r="U35" s="3">
         <v>1200</v>
       </c>
       <c r="V35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X35" s="3">
         <v>1500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1100</v>
-      </c>
-      <c r="X35" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>800</v>
       </c>
       <c r="Z35" s="3">
         <v>1200</v>
       </c>
       <c r="AA35" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC35" s="3">
         <v>1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3060,8 +3230,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3091,197 +3263,211 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="F41" s="3">
+        <v>70800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>68400</v>
+      </c>
+      <c r="H41" s="3">
+        <v>55100</v>
+      </c>
+      <c r="I41" s="3">
+        <v>79300</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K41" s="3">
         <v>9000</v>
       </c>
-      <c r="E41" s="3">
-        <v>10400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>11100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>10000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>11300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>9000</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>7000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>6900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>6900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9100</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>8600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>7400</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>61800</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>59600</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>69300</v>
+        <v>300</v>
       </c>
       <c r="H42" s="3">
-        <v>65100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>92400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>113000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>143900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>163500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>136600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>133600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>120800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>131400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>91400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>72300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>59300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>27300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>20300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>22800</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z42" s="3">
         <v>15900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>6300</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AC42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3340,31 +3526,37 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3423,31 +3615,37 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+        <v>2300</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3506,31 +3704,37 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>42400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>41400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>71400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>55700</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
+        <v>79700</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3589,174 +3793,192 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>3100</v>
+        <v>90900</v>
       </c>
       <c r="E47" s="3">
-        <v>3000</v>
+        <v>92000</v>
       </c>
       <c r="F47" s="3">
-        <v>3000</v>
+        <v>94300</v>
       </c>
       <c r="G47" s="3">
-        <v>3000</v>
+        <v>95800</v>
       </c>
       <c r="H47" s="3">
-        <v>2900</v>
+        <v>96800</v>
       </c>
       <c r="I47" s="3">
+        <v>102100</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>2800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>2700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>2600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>2400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2300</v>
       </c>
       <c r="P47" s="3">
         <v>2400</v>
       </c>
       <c r="Q47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S47" s="3">
         <v>2100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>1900</v>
-      </c>
-      <c r="V47" s="3">
-        <v>1800</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="X47" s="3">
         <v>1800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1700</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F48" s="3">
         <v>14600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>14700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>14500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>14500</v>
       </c>
-      <c r="H48" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I48" s="3">
-        <v>14100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>14100</v>
+      <c r="J48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K48" s="3">
         <v>14100</v>
       </c>
       <c r="L48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="M48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="N48" s="3">
         <v>14200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>14400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>14400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>13900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>13300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>13600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>13600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>13400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>12900</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>12400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>11900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3838,8 +4060,14 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3921,8 +4149,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4004,31 +4238,37 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>16600</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>15500</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>13300</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>14400</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+        <v>13900</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4087,8 +4327,14 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4170,91 +4416,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>818000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>794300</v>
+      </c>
+      <c r="F54" s="3">
         <v>802200</v>
       </c>
-      <c r="E54" s="3">
-        <v>791000</v>
-      </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>789000</v>
+      </c>
+      <c r="H54" s="3">
         <v>741900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>746800</v>
       </c>
-      <c r="H54" s="3">
-        <v>714800</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>715500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>707000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>717400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>700500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>663800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>655100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>645300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>641100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>597800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>586700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>576700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>513100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>492800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>484600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>457700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>434800</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4284,8 +4542,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4315,105 +4575,113 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>5</v>
+      <c r="D57" s="3">
+        <v>708800</v>
       </c>
       <c r="E57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>5</v>
+        <v>687900</v>
+      </c>
+      <c r="F57" s="3">
+        <v>701400</v>
+      </c>
+      <c r="G57" s="3">
+        <v>689600</v>
+      </c>
+      <c r="H57" s="3">
+        <v>651600</v>
       </c>
       <c r="I57" s="3">
+        <v>658400</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>300</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4481,31 +4749,37 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -4564,31 +4838,37 @@
       <c r="AC59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>727800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>706900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>720400</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>710200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>651600</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+        <v>658400</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4647,29 +4927,35 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>14000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>14000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -4677,19 +4963,19 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
         <v>3000</v>
       </c>
       <c r="O61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="P61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="Q61" s="3">
         <v>4000</v>
@@ -4698,23 +4984,23 @@
         <v>4000</v>
       </c>
       <c r="S61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T61" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U61" s="3">
         <v>10000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>10000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>5000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>5000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4728,33 +5014,39 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>9100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>5700</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>4300</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4813,8 +5105,14 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4896,8 +5194,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4979,8 +5283,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5062,91 +5372,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>736600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>716000</v>
+      </c>
+      <c r="F66" s="3">
         <v>726100</v>
       </c>
-      <c r="E66" s="3">
-        <v>716200</v>
-      </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>714200</v>
+      </c>
+      <c r="H66" s="3">
         <v>670800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>676700</v>
       </c>
-      <c r="H66" s="3">
-        <v>646200</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>649100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>649000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>659900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>641100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>604600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>596600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>588500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>585600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>544000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>533700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>524600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>461900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>442500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>435100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>410500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>388500</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5176,8 +5498,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5259,8 +5583,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5342,8 +5672,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5366,10 +5702,10 @@
         <v>200</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -5425,8 +5761,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5508,91 +5850,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>56400</v>
+      </c>
+      <c r="F72" s="3">
         <v>54700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>53400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>52100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>50500</v>
       </c>
-      <c r="H72" s="3">
-        <v>48900</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>47700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>45800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>43900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>42500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>41300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>45100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>43600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>42400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>40700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>39700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>38900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>38000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>37300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>36300</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>34300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>33300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5674,8 +6028,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5757,8 +6117,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5840,91 +6206,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>81100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>78000</v>
+      </c>
+      <c r="F76" s="3">
         <v>75900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>74500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>70800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>69900</v>
       </c>
-      <c r="H76" s="3">
-        <v>68300</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>66100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
+        <v>66100</v>
+      </c>
+      <c r="L76" s="3">
         <v>57900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>57600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>59500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>59100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>58600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>56900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>55500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>53800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>53000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>52200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>51100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>50300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>49500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>47200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>46300</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6006,179 +6384,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="E81" s="3">
-        <v>1700</v>
+        <v>2200</v>
       </c>
       <c r="F81" s="3">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="G81" s="3">
-        <v>4000</v>
+        <v>1800</v>
       </c>
       <c r="H81" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="I81" s="3">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="J81" s="3">
         <v>2300</v>
       </c>
       <c r="K81" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M81" s="3">
         <v>1800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
-      </c>
-      <c r="S81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T81" s="3">
-        <v>1000</v>
       </c>
       <c r="U81" s="3">
         <v>1200</v>
       </c>
       <c r="V81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X81" s="3">
         <v>1500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1100</v>
-      </c>
-      <c r="X81" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>800</v>
       </c>
       <c r="Z81" s="3">
         <v>1200</v>
       </c>
       <c r="AA81" s="3">
+        <v>800</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC81" s="3">
         <v>1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6208,31 +6604,33 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6285,14 +6683,20 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6374,8 +6778,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6457,8 +6867,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6540,8 +6956,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6623,8 +7045,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6706,31 +7134,37 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -6783,14 +7217,20 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6820,31 +7260,33 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6897,14 +7339,20 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
+      <c r="AB91" s="3">
+        <v>0</v>
       </c>
       <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6986,8 +7434,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7069,31 +7523,37 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7146,14 +7606,20 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7183,31 +7649,33 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7266,8 +7734,14 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7349,8 +7823,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7432,8 +7912,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7515,31 +8001,37 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7592,37 +8084,43 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
+      <c r="AB100" s="3">
+        <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7681,31 +8179,37 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -7758,10 +8262,16 @@
       <c r="AA102" s="3">
         <v>0</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,225 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E8" s="3">
         <v>7500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>7500</v>
       </c>
       <c r="K8" s="3">
         <v>7500</v>
       </c>
       <c r="L8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="M8" s="3">
         <v>6900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5800</v>
-      </c>
-      <c r="N8" s="3">
-        <v>5500</v>
       </c>
       <c r="O8" s="3">
         <v>5500</v>
       </c>
       <c r="P8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Q8" s="3">
         <v>5700</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>5600</v>
       </c>
       <c r="R8" s="3">
         <v>5600</v>
       </c>
       <c r="S8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="T8" s="3">
         <v>22400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5700</v>
-      </c>
-      <c r="U8" s="3">
-        <v>5500</v>
       </c>
       <c r="V8" s="3">
         <v>5500</v>
       </c>
       <c r="W8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="X8" s="3">
         <v>5600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>4900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -962,35 +968,38 @@
       <c r="AE9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E10" s="3">
         <v>7500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7500</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1051,8 +1060,11 @@
       <c r="AE10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,8 +1096,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1173,8 +1186,11 @@
       <c r="AE12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1278,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1288,8 +1307,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1351,8 +1370,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1369,7 +1391,7 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>300</v>
@@ -1378,7 +1400,7 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1440,8 +1462,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,40 +1495,41 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5000</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4900</v>
       </c>
       <c r="F17" s="3">
         <v>4900</v>
       </c>
       <c r="G17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H17" s="3">
         <v>4500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4700</v>
       </c>
       <c r="I17" s="3">
         <v>4700</v>
       </c>
       <c r="J17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K17" s="3">
         <v>4600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
-      </c>
-      <c r="M17" s="3">
-        <v>700</v>
       </c>
       <c r="N17" s="3">
         <v>700</v>
@@ -1512,144 +1538,150 @@
         <v>700</v>
       </c>
       <c r="P17" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>1200</v>
       </c>
       <c r="AA17" s="3">
         <v>1200</v>
       </c>
       <c r="AB17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AC17" s="3">
         <v>900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E18" s="3">
         <v>2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5100</v>
-      </c>
-      <c r="N18" s="3">
-        <v>4800</v>
       </c>
       <c r="O18" s="3">
         <v>4800</v>
       </c>
       <c r="P18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="Q18" s="3">
         <v>4900</v>
       </c>
       <c r="R18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="S18" s="3">
         <v>4800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4200</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3800</v>
       </c>
       <c r="Z18" s="3">
         <v>3800</v>
       </c>
       <c r="AA18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3700</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>3800</v>
       </c>
       <c r="AC18" s="3">
         <v>3800</v>
       </c>
       <c r="AD18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AE18" s="3">
         <v>3600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,13 +1713,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>200</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
@@ -1695,83 +1728,86 @@
       <c r="F20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-3300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2900</v>
       </c>
       <c r="N20" s="3">
         <v>-2900</v>
       </c>
       <c r="O20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="P20" s="3">
         <v>-3000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-2400</v>
       </c>
       <c r="Y20" s="3">
         <v>-2400</v>
       </c>
       <c r="Z20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1779,26 +1815,26 @@
         <v>2700</v>
       </c>
       <c r="E21" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>2800</v>
       </c>
       <c r="I21" s="3">
         <v>2800</v>
       </c>
       <c r="J21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K21" s="3">
         <v>3100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1856,11 +1892,14 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,8 +1924,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1948,97 +1987,103 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E23" s="3">
         <v>2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>2300</v>
       </c>
       <c r="G23" s="3">
         <v>2300</v>
       </c>
       <c r="H23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I23" s="3">
         <v>2600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1800</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1400</v>
       </c>
       <c r="Z23" s="3">
         <v>1400</v>
       </c>
       <c r="AA23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2046,10 +2091,10 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
@@ -2061,10 +2106,10 @@
         <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
         <v>600</v>
-      </c>
-      <c r="K24" s="3">
-        <v>500</v>
       </c>
       <c r="L24" s="3">
         <v>500</v>
@@ -2073,37 +2118,37 @@
         <v>500</v>
       </c>
       <c r="N24" s="3">
+        <v>500</v>
+      </c>
+      <c r="O24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>300</v>
-      </c>
-      <c r="P24" s="3">
-        <v>400</v>
       </c>
       <c r="Q24" s="3">
         <v>400</v>
       </c>
       <c r="R24" s="3">
+        <v>400</v>
+      </c>
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>300</v>
       </c>
       <c r="V24" s="3">
         <v>300</v>
       </c>
       <c r="W24" s="3">
+        <v>300</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
-      </c>
-      <c r="X24" s="3">
-        <v>300</v>
       </c>
       <c r="Y24" s="3">
         <v>300</v>
@@ -2112,22 +2157,25 @@
         <v>300</v>
       </c>
       <c r="AA24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB24" s="3">
         <v>200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>300</v>
       </c>
       <c r="AC24" s="3">
         <v>300</v>
       </c>
       <c r="AD24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,8 +2263,11 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2224,88 +2275,91 @@
         <v>2000</v>
       </c>
       <c r="E26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F26" s="3">
         <v>2200</v>
-      </c>
-      <c r="F26" s="3">
-        <v>1800</v>
       </c>
       <c r="G26" s="3">
         <v>1800</v>
       </c>
       <c r="H26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I26" s="3">
         <v>2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1800</v>
-      </c>
-      <c r="N26" s="3">
-        <v>1500</v>
       </c>
       <c r="O26" s="3">
         <v>1500</v>
       </c>
       <c r="P26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>1100</v>
       </c>
       <c r="AD26" s="3">
         <v>1100</v>
       </c>
       <c r="AE26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2313,88 +2367,91 @@
         <v>1800</v>
       </c>
       <c r="E27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F27" s="3">
         <v>2100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>1700</v>
       </c>
       <c r="G27" s="3">
         <v>1700</v>
       </c>
       <c r="H27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I27" s="3">
         <v>2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2200</v>
       </c>
       <c r="K27" s="3">
         <v>2200</v>
       </c>
       <c r="L27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1800</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1500</v>
       </c>
       <c r="O27" s="3">
         <v>1500</v>
       </c>
       <c r="P27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>1100</v>
       </c>
       <c r="AD27" s="3">
         <v>1100</v>
       </c>
       <c r="AE27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2539,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2631,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2723,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,13 +2815,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>-200</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
@@ -2763,83 +2832,86 @@
       <c r="F32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>3300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2900</v>
       </c>
       <c r="N32" s="3">
         <v>2900</v>
       </c>
       <c r="O32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="P32" s="3">
         <v>3000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2600</v>
-      </c>
-      <c r="X32" s="3">
-        <v>2400</v>
       </c>
       <c r="Y32" s="3">
         <v>2400</v>
       </c>
       <c r="Z32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AA32" s="3">
         <v>2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2847,88 +2919,91 @@
         <v>2000</v>
       </c>
       <c r="E33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F33" s="3">
         <v>2200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>1800</v>
       </c>
       <c r="G33" s="3">
         <v>1800</v>
       </c>
       <c r="H33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I33" s="3">
         <v>2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1800</v>
-      </c>
-      <c r="N33" s="3">
-        <v>1500</v>
       </c>
       <c r="O33" s="3">
         <v>1500</v>
       </c>
       <c r="P33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>1100</v>
       </c>
       <c r="AD33" s="3">
         <v>1100</v>
       </c>
       <c r="AE33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,8 +3091,11 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3025,182 +3103,188 @@
         <v>2000</v>
       </c>
       <c r="E35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F35" s="3">
         <v>2200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1800</v>
       </c>
       <c r="G35" s="3">
         <v>1800</v>
       </c>
       <c r="H35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I35" s="3">
         <v>2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1800</v>
-      </c>
-      <c r="N35" s="3">
-        <v>1500</v>
       </c>
       <c r="O35" s="3">
         <v>1500</v>
       </c>
       <c r="P35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>1100</v>
       </c>
       <c r="AD35" s="3">
         <v>1100</v>
       </c>
       <c r="AE35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3316,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3350,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E41" s="3">
         <v>41800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>70800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>68400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>55100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>79300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L41" s="3">
         <v>9000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8100</v>
-      </c>
-      <c r="V41" s="3">
-        <v>6900</v>
       </c>
       <c r="W41" s="3">
         <v>6900</v>
       </c>
       <c r="X41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Y41" s="3">
         <v>9100</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>8600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7400</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AE41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3369,11 +3458,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -3381,70 +3470,73 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>92400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>113000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>143900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>163500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>136600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>133600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>120800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>131400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>91400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>72300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>59300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>27300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>20300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>22800</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z42" s="3">
+      <c r="Z42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA42" s="3">
         <v>15900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>6300</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AE42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3469,8 +3561,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3532,8 +3624,11 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3558,8 +3653,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3621,13 +3716,16 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
+      <c r="D45" s="3">
+        <v>2600</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>5</v>
@@ -3635,20 +3733,20 @@
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -3710,34 +3808,37 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E46" s="3">
         <v>42400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>41400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>71400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>72000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>79700</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K46" s="3">
-        <v>0</v>
+      <c r="K46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -3799,86 +3900,89 @@
       <c r="AE46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86400</v>
+      </c>
+      <c r="E47" s="3">
         <v>90900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>92000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>94300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>95800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>96800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>102100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>2800</v>
-      </c>
-      <c r="L47" s="3">
-        <v>2700</v>
       </c>
       <c r="M47" s="3">
         <v>2700</v>
       </c>
       <c r="N47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O47" s="3">
         <v>2600</v>
-      </c>
-      <c r="O47" s="3">
-        <v>2400</v>
       </c>
       <c r="P47" s="3">
         <v>2400</v>
       </c>
       <c r="Q47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R47" s="3">
         <v>2300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2400</v>
-      </c>
-      <c r="S47" s="3">
-        <v>2100</v>
       </c>
       <c r="T47" s="3">
         <v>2100</v>
       </c>
       <c r="U47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="V47" s="3">
         <v>2000</v>
       </c>
       <c r="W47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X47" s="3">
         <v>1900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1800</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>1800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1700</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3888,34 +3992,37 @@
       <c r="AE47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E48" s="3">
         <v>15200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>14500</v>
       </c>
       <c r="I48" s="3">
         <v>14500</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
-        <v>14100</v>
+      <c r="J48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L48" s="3">
         <v>14100</v>
@@ -3924,61 +4031,64 @@
         <v>14100</v>
       </c>
       <c r="N48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="O48" s="3">
         <v>14200</v>
-      </c>
-      <c r="O48" s="3">
-        <v>14400</v>
       </c>
       <c r="P48" s="3">
         <v>14400</v>
       </c>
       <c r="Q48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="R48" s="3">
         <v>13900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13400</v>
-      </c>
-      <c r="T48" s="3">
-        <v>13600</v>
       </c>
       <c r="U48" s="3">
         <v>13600</v>
       </c>
       <c r="V48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="W48" s="3">
         <v>13500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>12900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>12400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11900</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4066,8 +4176,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4268,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,34 +4360,37 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E52" s="3">
         <v>19000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13900</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4333,8 +4452,11 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4544,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>857100</v>
+      </c>
+      <c r="E54" s="3">
         <v>818000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>794300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>802200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>789000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>741900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>746800</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>715500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>707000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>717400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>700500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>663800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>655100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>645300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>641100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>597800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>586700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>576700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>513100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>492800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>484600</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>457700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>434800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AE54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4672,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,102 +4706,106 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>767200</v>
+      </c>
+      <c r="E57" s="3">
         <v>708800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>687900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>701400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>689600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>651600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>658400</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>300</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>500</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AE57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>19000</v>
@@ -4684,7 +4817,7 @@
         <v>19000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -4755,8 +4888,11 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4781,8 +4917,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -4844,34 +4980,37 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>770800</v>
+      </c>
+      <c r="E60" s="3">
         <v>727800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>706900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>720400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>710200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>651600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>658400</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -4933,8 +5072,11 @@
       <c r="AE60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4951,13 +5093,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>14000</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4969,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>3000</v>
@@ -4978,7 +5120,7 @@
         <v>3000</v>
       </c>
       <c r="Q61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="R61" s="3">
         <v>4000</v>
@@ -4990,19 +5132,19 @@
         <v>4000</v>
       </c>
       <c r="U61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="V61" s="3">
         <v>10000</v>
       </c>
       <c r="W61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="X61" s="3">
         <v>5000</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -5020,36 +5162,39 @@
         <v>0</v>
       </c>
       <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E62" s="3">
         <v>8800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4300</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -5111,8 +5256,11 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5348,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5440,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5532,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>774600</v>
+      </c>
+      <c r="E66" s="3">
         <v>736600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>716000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>726100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>714200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>670800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>676700</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>649100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>649000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>659900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>641100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>604600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>596600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>588500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>585600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>544000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>533700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>524600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>461900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>442500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>435100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>410500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>388500</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AE66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5660,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5750,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5842,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5708,7 +5875,7 @@
         <v>200</v>
       </c>
       <c r="L70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M70" s="3">
         <v>0</v>
@@ -5767,8 +5934,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6026,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59300</v>
+      </c>
+      <c r="E72" s="3">
         <v>57800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>56400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>54700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>50500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>47700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>43900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>42500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>43600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>42400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>40700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>39700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>38900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>37300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>36300</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>34300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>33300</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6210,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6302,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6394,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>82300</v>
+      </c>
+      <c r="E76" s="3">
         <v>81100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>78000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>75900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>74500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>70800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>69900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>66100</v>
       </c>
       <c r="K76" s="3">
         <v>66100</v>
       </c>
       <c r="L76" s="3">
+        <v>66100</v>
+      </c>
+      <c r="M76" s="3">
         <v>57900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>57600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>59500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>59100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>56900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>53800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>51100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>50300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>47200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>46300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AD76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AE76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,102 +6578,108 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6493,88 +6687,91 @@
         <v>2000</v>
       </c>
       <c r="E81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F81" s="3">
         <v>2200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>1800</v>
       </c>
       <c r="G81" s="3">
         <v>1800</v>
       </c>
       <c r="H81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I81" s="3">
         <v>2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1800</v>
-      </c>
-      <c r="N81" s="3">
-        <v>1500</v>
       </c>
       <c r="O81" s="3">
         <v>1500</v>
       </c>
       <c r="P81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>1100</v>
       </c>
       <c r="AD81" s="3">
         <v>1100</v>
       </c>
       <c r="AE81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6803,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6632,8 +6830,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6689,14 +6887,17 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6985,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7077,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7169,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7261,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,8 +7353,11 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7166,8 +7382,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -7223,14 +7439,17 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7481,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7288,8 +7508,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -7345,14 +7565,17 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7663,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +7755,11 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7555,8 +7784,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -7612,14 +7841,17 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7883,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7677,8 +7910,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7740,8 +7973,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8065,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8157,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8249,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8033,8 +8278,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -8090,14 +8335,17 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8122,8 +8370,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8185,8 +8433,11 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8211,8 +8462,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -8268,10 +8519,13 @@
       <c r="AC102" s="3">
         <v>0</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,231 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="E8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F8" s="3">
         <v>7500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>7500</v>
       </c>
       <c r="L8" s="3">
         <v>7500</v>
       </c>
       <c r="M8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="N8" s="3">
         <v>6900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5800</v>
-      </c>
-      <c r="O8" s="3">
-        <v>5500</v>
       </c>
       <c r="P8" s="3">
         <v>5500</v>
       </c>
       <c r="Q8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="R8" s="3">
         <v>5700</v>
-      </c>
-      <c r="R8" s="3">
-        <v>5600</v>
       </c>
       <c r="S8" s="3">
         <v>5600</v>
       </c>
       <c r="T8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="U8" s="3">
         <v>22400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5700</v>
-      </c>
-      <c r="V8" s="3">
-        <v>5500</v>
       </c>
       <c r="W8" s="3">
         <v>5500</v>
       </c>
       <c r="X8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Y8" s="3">
         <v>5600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -971,38 +978,41 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8000</v>
+        <v>8300</v>
       </c>
       <c r="E10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F10" s="3">
         <v>7500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>7100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>7500</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1063,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1189,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1310,8 +1330,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1373,16 +1393,19 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
@@ -1394,7 +1417,7 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>300</v>
@@ -1403,7 +1426,7 @@
         <v>300</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1465,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,43 +1522,44 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5400</v>
+        <v>5700</v>
       </c>
       <c r="E17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F17" s="3">
         <v>5000</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4900</v>
       </c>
       <c r="G17" s="3">
         <v>4900</v>
       </c>
       <c r="H17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I17" s="3">
         <v>4500</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4700</v>
       </c>
       <c r="J17" s="3">
         <v>4700</v>
       </c>
       <c r="K17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L17" s="3">
         <v>4600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
-      </c>
-      <c r="N17" s="3">
-        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>700</v>
@@ -1541,55 +1568,58 @@
         <v>700</v>
       </c>
       <c r="Q17" s="3">
+        <v>700</v>
+      </c>
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>1200</v>
       </c>
       <c r="AB17" s="3">
         <v>1200</v>
       </c>
       <c r="AC17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AD17" s="3">
         <v>900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1597,91 +1627,94 @@
         <v>2600</v>
       </c>
       <c r="E18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F18" s="3">
         <v>2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>4800</v>
       </c>
       <c r="P18" s="3">
         <v>4800</v>
       </c>
       <c r="Q18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="R18" s="3">
         <v>4900</v>
       </c>
       <c r="S18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="T18" s="3">
         <v>4800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4200</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>3800</v>
       </c>
       <c r="AA18" s="3">
         <v>3800</v>
       </c>
       <c r="AB18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AC18" s="3">
         <v>3700</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>3800</v>
       </c>
       <c r="AD18" s="3">
         <v>3800</v>
       </c>
       <c r="AE18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF18" s="3">
         <v>3600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,16 +1747,17 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>200</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>500</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>5</v>
@@ -1731,113 +1765,116 @@
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-3300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-2900</v>
       </c>
       <c r="O20" s="3">
         <v>-2900</v>
       </c>
       <c r="P20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-2400</v>
       </c>
       <c r="Z20" s="3">
         <v>-2400</v>
       </c>
       <c r="AA20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>2700</v>
       </c>
-      <c r="E21" s="3">
-        <v>2700</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>2800</v>
       </c>
       <c r="J21" s="3">
         <v>2800</v>
       </c>
       <c r="K21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L21" s="3">
         <v>3100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1895,11 +1932,14 @@
       <c r="AE21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1927,8 +1967,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1990,100 +2030,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E23" s="3">
         <v>2500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>2300</v>
       </c>
       <c r="H23" s="3">
         <v>2300</v>
       </c>
       <c r="I23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J23" s="3">
         <v>2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1800</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1400</v>
       </c>
       <c r="AA23" s="3">
         <v>1400</v>
       </c>
       <c r="AB23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2094,10 +2140,10 @@
         <v>500</v>
       </c>
       <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>500</v>
@@ -2109,10 +2155,10 @@
         <v>500</v>
       </c>
       <c r="K24" s="3">
+        <v>500</v>
+      </c>
+      <c r="L24" s="3">
         <v>600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>500</v>
       </c>
       <c r="M24" s="3">
         <v>500</v>
@@ -2121,37 +2167,37 @@
         <v>500</v>
       </c>
       <c r="O24" s="3">
+        <v>500</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>300</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>400</v>
       </c>
       <c r="R24" s="3">
         <v>400</v>
       </c>
       <c r="S24" s="3">
+        <v>400</v>
+      </c>
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
-      </c>
-      <c r="V24" s="3">
-        <v>300</v>
       </c>
       <c r="W24" s="3">
         <v>300</v>
       </c>
       <c r="X24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>300</v>
       </c>
       <c r="Z24" s="3">
         <v>300</v>
@@ -2160,22 +2206,25 @@
         <v>300</v>
       </c>
       <c r="AB24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>300</v>
       </c>
       <c r="AD24" s="3">
         <v>300</v>
       </c>
       <c r="AE24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,8 +2315,11 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2278,180 +2330,186 @@
         <v>2000</v>
       </c>
       <c r="F26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G26" s="3">
         <v>2200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>1800</v>
       </c>
       <c r="H26" s="3">
         <v>1800</v>
       </c>
       <c r="I26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J26" s="3">
         <v>2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1500</v>
       </c>
       <c r="P26" s="3">
         <v>1500</v>
       </c>
       <c r="Q26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>1100</v>
       </c>
       <c r="AE26" s="3">
         <v>1100</v>
       </c>
       <c r="AF26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="E27" s="3">
         <v>1800</v>
       </c>
       <c r="F27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G27" s="3">
         <v>2100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>1700</v>
       </c>
       <c r="H27" s="3">
         <v>1700</v>
       </c>
       <c r="I27" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J27" s="3">
         <v>2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1900</v>
-      </c>
-      <c r="K27" s="3">
-        <v>2200</v>
       </c>
       <c r="L27" s="3">
         <v>2200</v>
       </c>
       <c r="M27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
-      </c>
-      <c r="O27" s="3">
-        <v>1500</v>
       </c>
       <c r="P27" s="3">
         <v>1500</v>
       </c>
       <c r="Q27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>1100</v>
       </c>
       <c r="AE27" s="3">
         <v>1100</v>
       </c>
       <c r="AF27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,16 +2885,19 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-500</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>5</v>
@@ -2835,83 +2905,86 @@
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>3300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3100</v>
-      </c>
-      <c r="N32" s="3">
-        <v>2900</v>
       </c>
       <c r="O32" s="3">
         <v>2900</v>
       </c>
       <c r="P32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Q32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>2400</v>
       </c>
       <c r="Z32" s="3">
         <v>2400</v>
       </c>
       <c r="AA32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB32" s="3">
         <v>2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2922,88 +2995,91 @@
         <v>2000</v>
       </c>
       <c r="F33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G33" s="3">
         <v>2200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>1800</v>
       </c>
       <c r="H33" s="3">
         <v>1800</v>
       </c>
       <c r="I33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J33" s="3">
         <v>2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1500</v>
       </c>
       <c r="P33" s="3">
         <v>1500</v>
       </c>
       <c r="Q33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>1100</v>
       </c>
       <c r="AE33" s="3">
         <v>1100</v>
       </c>
       <c r="AF33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,8 +3170,11 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3106,185 +3185,191 @@
         <v>2000</v>
       </c>
       <c r="F35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G35" s="3">
         <v>2200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>1800</v>
       </c>
       <c r="H35" s="3">
         <v>1800</v>
       </c>
       <c r="I35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J35" s="3">
         <v>2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1500</v>
       </c>
       <c r="P35" s="3">
         <v>1500</v>
       </c>
       <c r="Q35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>1100</v>
       </c>
       <c r="AE35" s="3">
         <v>1100</v>
       </c>
       <c r="AF35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>66800</v>
+        <v>61200</v>
       </c>
       <c r="E41" s="3">
+        <v>65500</v>
+      </c>
+      <c r="F41" s="3">
         <v>41800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>70800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>68400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>55100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>79300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M41" s="3">
         <v>9000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8100</v>
-      </c>
-      <c r="W41" s="3">
-        <v>6900</v>
       </c>
       <c r="X41" s="3">
         <v>6900</v>
       </c>
       <c r="Y41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Z41" s="3">
         <v>9100</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>8600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3452,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3461,11 +3551,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3473,70 +3563,73 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>92400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>113000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>143900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>163500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>136600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>133600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>120800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>131400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>91400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>72300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>59300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>27300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>20300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>22800</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3">
         <v>15900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6300</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3564,8 +3657,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3627,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3656,8 +3752,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3719,37 +3815,40 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3">
         <v>2600</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3">
         <v>2300</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -3811,37 +3910,40 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>70000</v>
+        <v>61200</v>
       </c>
       <c r="E46" s="3">
+        <v>69400</v>
+      </c>
+      <c r="F46" s="3">
         <v>42400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>71400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>72000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>79700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
+      <c r="L46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -3903,89 +4005,92 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>86400</v>
+        <v>82900</v>
       </c>
       <c r="E47" s="3">
+        <v>83300</v>
+      </c>
+      <c r="F47" s="3">
         <v>90900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>92000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>94300</v>
       </c>
-      <c r="H47" s="3">
-        <v>95800</v>
-      </c>
       <c r="I47" s="3">
+        <v>95600</v>
+      </c>
+      <c r="J47" s="3">
         <v>96800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>102100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
         <v>2800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>2700</v>
       </c>
       <c r="N47" s="3">
         <v>2700</v>
       </c>
       <c r="O47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P47" s="3">
         <v>2600</v>
-      </c>
-      <c r="P47" s="3">
-        <v>2400</v>
       </c>
       <c r="Q47" s="3">
         <v>2400</v>
       </c>
       <c r="R47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S47" s="3">
         <v>2300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2400</v>
-      </c>
-      <c r="T47" s="3">
-        <v>2100</v>
       </c>
       <c r="U47" s="3">
         <v>2100</v>
       </c>
       <c r="V47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="W47" s="3">
         <v>2000</v>
       </c>
       <c r="X47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y47" s="3">
         <v>1900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1800</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>1800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1700</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3995,37 +4100,40 @@
       <c r="AF47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E48" s="3">
         <v>17400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>14500</v>
       </c>
       <c r="J48" s="3">
         <v>14500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3">
-        <v>14100</v>
+      <c r="K48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M48" s="3">
         <v>14100</v>
@@ -4034,61 +4142,64 @@
         <v>14100</v>
       </c>
       <c r="O48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="P48" s="3">
         <v>14200</v>
-      </c>
-      <c r="P48" s="3">
-        <v>14400</v>
       </c>
       <c r="Q48" s="3">
         <v>14400</v>
       </c>
       <c r="R48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="S48" s="3">
         <v>13900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13400</v>
-      </c>
-      <c r="U48" s="3">
-        <v>13600</v>
       </c>
       <c r="V48" s="3">
         <v>13600</v>
       </c>
       <c r="W48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="X48" s="3">
         <v>13500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12900</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>12400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11900</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4179,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,37 +4480,40 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11700</v>
+        <v>16600</v>
       </c>
       <c r="E52" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F52" s="3">
         <v>19000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>16600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15500</v>
       </c>
-      <c r="H52" s="3">
-        <v>13300</v>
-      </c>
       <c r="I52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="J52" s="3">
         <v>14400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>13900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4455,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>865400</v>
+      </c>
+      <c r="E54" s="3">
         <v>857100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>818000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>794300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>802200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>789000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>741900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>746800</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M54" s="3">
         <v>715500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>707000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>717400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>700500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>663800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>655100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>645300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>641100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>597800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>586700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>576700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>513100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>492800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>484600</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>457700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>434800</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>773200</v>
+      </c>
+      <c r="E57" s="3">
         <v>767200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>708800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>687900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>701400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>689600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>651600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>658400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X57" s="3">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4808,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>19000</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>19000</v>
@@ -4820,7 +4954,7 @@
         <v>19000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -4891,8 +5025,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4920,8 +5057,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -4983,37 +5120,40 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>773200</v>
+      </c>
+      <c r="E60" s="3">
         <v>770800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>727800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>706900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>720400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>710200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>651600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>658400</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
+      <c r="L60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5075,8 +5215,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5096,13 +5239,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>14000</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -5114,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>3000</v>
@@ -5123,7 +5266,7 @@
         <v>3000</v>
       </c>
       <c r="R61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="S61" s="3">
         <v>4000</v>
@@ -5135,19 +5278,19 @@
         <v>4000</v>
       </c>
       <c r="V61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="W61" s="3">
         <v>10000</v>
       </c>
       <c r="X61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Y61" s="3">
         <v>5000</v>
       </c>
       <c r="Z61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AA61" s="3">
         <v>0</v>
@@ -5165,39 +5308,42 @@
         <v>0</v>
       </c>
       <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3800</v>
+        <v>7400</v>
       </c>
       <c r="E62" s="3">
+        <v>3700</v>
+      </c>
+      <c r="F62" s="3">
         <v>8800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4300</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5259,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>780600</v>
+      </c>
+      <c r="E66" s="3">
         <v>774600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>736600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>716000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>726100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>714200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>670800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>676700</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M66" s="3">
         <v>649100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>649000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>659900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>641100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>604600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>596600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>588500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>585600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>544000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>533700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>524600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>461900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>442500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>435100</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>410500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>388500</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5878,7 +6046,7 @@
         <v>200</v>
       </c>
       <c r="M70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="N70" s="3">
         <v>0</v>
@@ -5937,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E72" s="3">
         <v>59300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>56400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>50500</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M72" s="3">
         <v>47700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>43900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>42500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>41300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>43600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>42400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>40700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>39700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>38900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>37300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>36300</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>34300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>33300</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E76" s="3">
         <v>82300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>81100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>78000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>75900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>74500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>70800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>69900</v>
-      </c>
-      <c r="K76" s="3">
-        <v>66100</v>
       </c>
       <c r="L76" s="3">
         <v>66100</v>
       </c>
       <c r="M76" s="3">
+        <v>66100</v>
+      </c>
+      <c r="N76" s="3">
         <v>57900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>57600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>59500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>56900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>55500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>53800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>52200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>51100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>50300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>49500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>47200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>46300</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,105 +6770,111 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6690,88 +6885,91 @@
         <v>2000</v>
       </c>
       <c r="F81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G81" s="3">
         <v>2200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>1800</v>
       </c>
       <c r="H81" s="3">
         <v>1800</v>
       </c>
       <c r="I81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J81" s="3">
         <v>2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1500</v>
       </c>
       <c r="P81" s="3">
         <v>1500</v>
       </c>
       <c r="Q81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1200</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>1100</v>
       </c>
       <c r="AE81" s="3">
         <v>1100</v>
       </c>
       <c r="AF81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6833,8 +7032,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6890,14 +7089,17 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF83" s="3">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7385,8 +7602,8 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -7442,14 +7659,17 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF89" s="3">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7511,8 +7732,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7568,14 +7789,17 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-      <c r="AE91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7787,8 +8017,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7844,14 +8074,17 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7913,8 +8147,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7976,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8281,8 +8527,8 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -8338,14 +8584,17 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF100" s="3">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8373,8 +8622,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -8436,8 +8685,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8465,8 +8717,8 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -8522,10 +8774,13 @@
       <c r="AD102" s="3">
         <v>0</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF102" s="3">
+      <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>6200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BORT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="92">
   <si>
     <t>BORT</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>8100</v>
       </c>
-      <c r="F8" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K8" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L8" s="3">
         <v>7200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K8" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L8" s="3">
-        <v>7500</v>
       </c>
       <c r="M8" s="3">
         <v>7500</v>
       </c>
       <c r="N8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="O8" s="3">
         <v>6900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5800</v>
-      </c>
-      <c r="P8" s="3">
-        <v>5500</v>
       </c>
       <c r="Q8" s="3">
         <v>5500</v>
       </c>
       <c r="R8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S8" s="3">
         <v>5700</v>
-      </c>
-      <c r="S8" s="3">
-        <v>5600</v>
       </c>
       <c r="T8" s="3">
         <v>5600</v>
       </c>
       <c r="U8" s="3">
+        <v>5600</v>
+      </c>
+      <c r="V8" s="3">
         <v>22400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5700</v>
-      </c>
-      <c r="W8" s="3">
-        <v>5500</v>
       </c>
       <c r="X8" s="3">
         <v>5500</v>
       </c>
       <c r="Y8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="Z8" s="3">
         <v>5600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>4600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,41 +988,44 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
         <v>8100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="M10" s="3">
         <v>7500</v>
       </c>
-      <c r="G10" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>7200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>7100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>7300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>7200</v>
-      </c>
-      <c r="L10" s="3">
-        <v>7500</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1333,8 +1353,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1396,31 +1416,34 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>300</v>
       </c>
-      <c r="E15" s="3">
-        <v>300</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>200</v>
-      </c>
-      <c r="H15" s="3">
-        <v>200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
@@ -1429,7 +1452,7 @@
         <v>300</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,46 +1549,47 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>5700</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
         <v>5100</v>
       </c>
-      <c r="F17" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
         <v>4500</v>
-      </c>
-      <c r="J17" s="3">
-        <v>4700</v>
       </c>
       <c r="K17" s="3">
         <v>4700</v>
       </c>
       <c r="L17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M17" s="3">
         <v>4600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
-      </c>
-      <c r="O17" s="3">
-        <v>700</v>
       </c>
       <c r="P17" s="3">
         <v>700</v>
@@ -1571,150 +1598,156 @@
         <v>700</v>
       </c>
       <c r="R17" s="3">
+        <v>700</v>
+      </c>
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>1200</v>
       </c>
       <c r="AC17" s="3">
         <v>1200</v>
       </c>
       <c r="AD17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE17" s="3">
         <v>900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K18" s="3">
         <v>2600</v>
       </c>
-      <c r="E18" s="3">
-        <v>3000</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>2800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I18" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>4800</v>
       </c>
       <c r="Q18" s="3">
         <v>4800</v>
       </c>
       <c r="R18" s="3">
-        <v>4900</v>
+        <v>4800</v>
       </c>
       <c r="S18" s="3">
         <v>4900</v>
       </c>
       <c r="T18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="U18" s="3">
         <v>4800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4200</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>3800</v>
       </c>
       <c r="AB18" s="3">
         <v>3800</v>
       </c>
       <c r="AC18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD18" s="3">
         <v>3700</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>3800</v>
       </c>
       <c r="AE18" s="3">
         <v>3800</v>
       </c>
       <c r="AF18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AG18" s="3">
         <v>3600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,136 +1781,140 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-3300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-2900</v>
       </c>
       <c r="P20" s="3">
         <v>-2900</v>
       </c>
       <c r="Q20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R20" s="3">
         <v>-3000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-10000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2600</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-2400</v>
       </c>
       <c r="AA20" s="3">
         <v>-2400</v>
       </c>
       <c r="AB20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>2800</v>
       </c>
-      <c r="E21" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>2700</v>
-      </c>
       <c r="G21" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>2600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>2800</v>
       </c>
       <c r="K21" s="3">
         <v>2800</v>
       </c>
       <c r="L21" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M21" s="3">
         <v>3100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1935,11 +1972,14 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH21" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,8 +2010,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2033,123 +2073,129 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K23" s="3">
         <v>2600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="L23" s="3">
         <v>2500</v>
       </c>
-      <c r="F23" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="M23" s="3">
+        <v>2900</v>
+      </c>
+      <c r="N23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="O23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>2600</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="P23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S23" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T23" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="L23" s="3">
-        <v>2900</v>
-      </c>
-      <c r="M23" s="3">
-        <v>2700</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="P23" s="3">
-        <v>1900</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="V23" s="3">
+        <v>5800</v>
+      </c>
+      <c r="W23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1800</v>
-      </c>
-      <c r="R23" s="3">
-        <v>2200</v>
-      </c>
-      <c r="S23" s="3">
-        <v>2000</v>
-      </c>
-      <c r="T23" s="3">
-        <v>2500</v>
-      </c>
-      <c r="U23" s="3">
-        <v>5800</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="X23" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>1800</v>
-      </c>
-      <c r="AA23" s="3">
-        <v>1400</v>
       </c>
       <c r="AB23" s="3">
         <v>1400</v>
       </c>
       <c r="AC23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>500</v>
-      </c>
-      <c r="E24" s="3">
-        <v>500</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
-        <v>600</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>500</v>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J24" s="3">
         <v>500</v>
@@ -2158,10 +2204,10 @@
         <v>500</v>
       </c>
       <c r="L24" s="3">
+        <v>500</v>
+      </c>
+      <c r="M24" s="3">
         <v>600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>500</v>
       </c>
       <c r="N24" s="3">
         <v>500</v>
@@ -2170,37 +2216,37 @@
         <v>500</v>
       </c>
       <c r="P24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>300</v>
-      </c>
-      <c r="R24" s="3">
-        <v>400</v>
       </c>
       <c r="S24" s="3">
         <v>400</v>
       </c>
       <c r="T24" s="3">
+        <v>400</v>
+      </c>
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>300</v>
       </c>
       <c r="X24" s="3">
         <v>300</v>
       </c>
       <c r="Y24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>300</v>
       </c>
       <c r="AA24" s="3">
         <v>300</v>
@@ -2209,22 +2255,25 @@
         <v>300</v>
       </c>
       <c r="AC24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD24" s="3">
         <v>200</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>300</v>
       </c>
       <c r="AE24" s="3">
         <v>300</v>
       </c>
       <c r="AF24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2000</v>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F26" s="3">
         <v>2000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L26" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N26" s="3">
         <v>2200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="O26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P26" s="3">
         <v>1800</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K26" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P26" s="3">
-        <v>1500</v>
       </c>
       <c r="Q26" s="3">
         <v>1500</v>
       </c>
       <c r="R26" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>1100</v>
       </c>
       <c r="AF26" s="3">
         <v>1100</v>
       </c>
       <c r="AG26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH26" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1800</v>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F27" s="3">
         <v>1800</v>
       </c>
-      <c r="G27" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="I27" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1900</v>
-      </c>
-      <c r="L27" s="3">
-        <v>2200</v>
       </c>
       <c r="M27" s="3">
         <v>2200</v>
       </c>
       <c r="N27" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
-      </c>
-      <c r="P27" s="3">
-        <v>1500</v>
       </c>
       <c r="Q27" s="3">
         <v>1500</v>
       </c>
       <c r="R27" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>1100</v>
       </c>
       <c r="AF27" s="3">
         <v>1100</v>
       </c>
       <c r="AG27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>3300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>2900</v>
       </c>
       <c r="P32" s="3">
         <v>2900</v>
       </c>
       <c r="Q32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="R32" s="3">
         <v>3000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>10000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2600</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>2400</v>
       </c>
       <c r="AA32" s="3">
         <v>2400</v>
       </c>
       <c r="AB32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC32" s="3">
         <v>2300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>2300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2000</v>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F33" s="3">
         <v>2000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L33" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N33" s="3">
         <v>2200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="O33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P33" s="3">
         <v>1800</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K33" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M33" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N33" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O33" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P33" s="3">
-        <v>1500</v>
       </c>
       <c r="Q33" s="3">
         <v>1500</v>
       </c>
       <c r="R33" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>1100</v>
       </c>
       <c r="AF33" s="3">
         <v>1100</v>
       </c>
       <c r="AG33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2000</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F35" s="3">
         <v>2000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L35" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N35" s="3">
         <v>2200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="O35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P35" s="3">
         <v>1800</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K35" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M35" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N35" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O35" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P35" s="3">
-        <v>1500</v>
       </c>
       <c r="Q35" s="3">
         <v>1500</v>
       </c>
       <c r="R35" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>1100</v>
       </c>
       <c r="AF35" s="3">
         <v>1100</v>
       </c>
       <c r="AG35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>61200</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
         <v>65500</v>
       </c>
-      <c r="F41" s="3">
-        <v>41800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>41100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>70800</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>68400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>79300</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="M41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N41" s="3">
         <v>9000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8100</v>
-      </c>
-      <c r="X41" s="3">
-        <v>6900</v>
       </c>
       <c r="Y41" s="3">
         <v>6900</v>
       </c>
       <c r="Z41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="AA41" s="3">
         <v>9100</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>8600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7400</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AG41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH41" s="3">
         <v>9600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3542,11 +3632,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3554,11 +3644,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3566,70 +3656,73 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>92400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>113000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>143900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>163500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>136600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>133600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>120800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>131400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>91400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>72300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>59300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>27300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>20300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>22800</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB42" s="3">
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>15900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>6300</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH42" s="3">
         <v>24200</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3660,8 +3753,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3755,8 +3851,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3818,40 +3914,43 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>2600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>2300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -3913,40 +4012,43 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>61200</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
         <v>69400</v>
       </c>
-      <c r="F46" s="3">
-        <v>42400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>41400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>71400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3">
         <v>72000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>79700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
-        <v>0</v>
+      <c r="M46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N46" s="3">
         <v>0</v>
@@ -4008,92 +4110,95 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>82900</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>83300</v>
       </c>
-      <c r="F47" s="3">
-        <v>90900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>92000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>94300</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>95600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>96800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>102100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>2800</v>
-      </c>
-      <c r="N47" s="3">
-        <v>2700</v>
       </c>
       <c r="O47" s="3">
         <v>2700</v>
       </c>
       <c r="P47" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q47" s="3">
         <v>2600</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>2400</v>
       </c>
       <c r="R47" s="3">
         <v>2400</v>
       </c>
       <c r="S47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T47" s="3">
         <v>2300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2400</v>
-      </c>
-      <c r="U47" s="3">
-        <v>2100</v>
       </c>
       <c r="V47" s="3">
         <v>2100</v>
       </c>
       <c r="W47" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="X47" s="3">
         <v>2000</v>
       </c>
       <c r="Y47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z47" s="3">
         <v>1900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1800</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1700</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4103,40 +4208,43 @@
       <c r="AG47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>17800</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>17400</v>
       </c>
-      <c r="F48" s="3">
-        <v>15200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>14900</v>
-      </c>
-      <c r="H48" s="3">
-        <v>14600</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>14700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>14500</v>
       </c>
       <c r="K48" s="3">
         <v>14500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M48" s="3">
-        <v>14100</v>
+      <c r="L48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N48" s="3">
         <v>14100</v>
@@ -4145,81 +4253,84 @@
         <v>14100</v>
       </c>
       <c r="P48" s="3">
+        <v>14100</v>
+      </c>
+      <c r="Q48" s="3">
         <v>14200</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>14400</v>
       </c>
       <c r="R48" s="3">
         <v>14400</v>
       </c>
       <c r="S48" s="3">
+        <v>14400</v>
+      </c>
+      <c r="T48" s="3">
         <v>13900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>13400</v>
-      </c>
-      <c r="V48" s="3">
-        <v>13600</v>
       </c>
       <c r="W48" s="3">
         <v>13600</v>
       </c>
       <c r="X48" s="3">
+        <v>13600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>13500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>12900</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>12400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11900</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,40 +4600,43 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>16600</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>15400</v>
       </c>
-      <c r="F52" s="3">
-        <v>19000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>16600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>15500</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>13500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>865400</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
         <v>857100</v>
       </c>
-      <c r="F54" s="3">
-        <v>818000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>794300</v>
-      </c>
-      <c r="H54" s="3">
-        <v>802200</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>789000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>741900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>746800</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="M54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N54" s="3">
         <v>715500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>707000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>717400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>700500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>663800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>655100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>645300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>641100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>597800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>586700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>576700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>513100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>492800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>484600</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>457700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>434800</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AG54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH54" s="3">
         <v>305700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,127 +4968,131 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>773200</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>767200</v>
       </c>
-      <c r="F57" s="3">
-        <v>708800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>687900</v>
-      </c>
-      <c r="H57" s="3">
-        <v>701400</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>689600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>651600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>658400</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AG57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH57" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3">
         <v>19000</v>
       </c>
-      <c r="G58" s="3">
-        <v>19000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>19000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>19000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -5028,8 +5162,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5060,8 +5197,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -5123,40 +5260,43 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>773200</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
         <v>770800</v>
       </c>
-      <c r="F60" s="3">
-        <v>727800</v>
-      </c>
-      <c r="G60" s="3">
-        <v>706900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>720400</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3">
         <v>710200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>651600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>658400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M60" s="3">
-        <v>0</v>
+      <c r="M60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N60" s="3">
         <v>0</v>
@@ -5218,8 +5358,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5242,13 +5385,13 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>14000</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5260,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>3000</v>
@@ -5269,7 +5412,7 @@
         <v>3000</v>
       </c>
       <c r="S61" s="3">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="T61" s="3">
         <v>4000</v>
@@ -5281,19 +5424,19 @@
         <v>4000</v>
       </c>
       <c r="W61" s="3">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="X61" s="3">
         <v>10000</v>
       </c>
       <c r="Y61" s="3">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="Z61" s="3">
         <v>5000</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AB61" s="3">
         <v>0</v>
@@ -5311,42 +5454,45 @@
         <v>0</v>
       </c>
       <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>7400</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>3700</v>
       </c>
-      <c r="F62" s="3">
-        <v>8800</v>
-      </c>
-      <c r="G62" s="3">
-        <v>9100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>5700</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>4000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4300</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>780600</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
         <v>774600</v>
       </c>
-      <c r="F66" s="3">
-        <v>736600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>716000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>726100</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>714200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>670800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>676700</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="M66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N66" s="3">
         <v>649100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>649000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>659900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>641100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>604600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>596600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>588500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>585600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>544000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>533700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>524600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>461900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>442500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>435100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>410500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>388500</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AG66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH66" s="3">
         <v>280300</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,28 +6178,31 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
         <v>200</v>
       </c>
       <c r="G70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
         <v>200</v>
@@ -6049,7 +6217,7 @@
         <v>200</v>
       </c>
       <c r="N70" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>60800</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>59300</v>
       </c>
-      <c r="F72" s="3">
-        <v>57800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>56400</v>
-      </c>
-      <c r="H72" s="3">
-        <v>54700</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>53400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>50500</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N72" s="3">
         <v>47700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>43900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>42500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>45100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>43600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>42400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>40700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>39700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>38900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>38000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>37300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>36300</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>34300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>84600</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3">
         <v>82300</v>
       </c>
-      <c r="F76" s="3">
-        <v>81100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>78000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>75900</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>74500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>70800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>69900</v>
-      </c>
-      <c r="L76" s="3">
-        <v>66100</v>
       </c>
       <c r="M76" s="3">
         <v>66100</v>
       </c>
       <c r="N76" s="3">
+        <v>66100</v>
+      </c>
+      <c r="O76" s="3">
         <v>57900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>57600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>59500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>59100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>56900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>53800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>53000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>51100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>50300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>49500</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>47200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>46300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AF76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AG76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH76" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>40999</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>2000</v>
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F81" s="3">
         <v>2000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L81" s="3">
+        <v>2000</v>
+      </c>
+      <c r="M81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N81" s="3">
         <v>2200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="O81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P81" s="3">
         <v>1800</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K81" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>2300</v>
-      </c>
-      <c r="M81" s="3">
-        <v>2200</v>
-      </c>
-      <c r="N81" s="3">
-        <v>2300</v>
-      </c>
-      <c r="O81" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P81" s="3">
-        <v>1500</v>
       </c>
       <c r="Q81" s="3">
         <v>1500</v>
       </c>
       <c r="R81" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1200</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>1100</v>
       </c>
       <c r="AF81" s="3">
         <v>1100</v>
       </c>
       <c r="AG81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7035,8 +7234,8 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7092,14 +7291,17 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH83" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +7787,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7605,8 +7822,8 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -7662,14 +7879,17 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7923,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7735,8 +7956,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7792,14 +8013,17 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8215,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8020,8 +8250,8 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -8077,14 +8307,17 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH94" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8150,8 +8384,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8741,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8530,8 +8776,8 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -8587,14 +8833,17 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-1500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8625,8 +8874,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -8688,8 +8937,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8720,8 +8972,8 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -8777,10 +9029,13 @@
       <c r="AE102" s="3">
         <v>0</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH102" s="3">
         <v>6200</v>
       </c>
     </row>
